--- a/01_Mechanic/02_Manufacturing/01_CNC/RP1_CNC_BOM.xlsx
+++ b/01_Mechanic/02_Manufacturing/01_CNC/RP1_CNC_BOM.xlsx
@@ -230,7 +230,7 @@
     <t>YCL.M000331</t>
   </si>
   <si>
-    <t>雷赛灵巧手转接件</t>
+    <t>灵巧手转接件</t>
   </si>
   <si>
     <t>YCL.M000332</t>

--- a/01_Mechanic/02_Manufacturing/01_CNC/RP1_CNC_BOM.xlsx
+++ b/01_Mechanic/02_Manufacturing/01_CNC/RP1_CNC_BOM.xlsx
@@ -230,7 +230,7 @@
     <t>YCL.M000331</t>
   </si>
   <si>
-    <t>灵巧手转接件</t>
+    <t>RP_Hand转接件</t>
   </si>
   <si>
     <t>YCL.M000332</t>
